--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230401_20231001.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230401_20231001.xlsx
@@ -1053,37 +1053,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>57.37704918032787</v>
       </c>
       <c r="C15" t="n">
-        <v>42.62295081967213</v>
+        <v>40.16393442622951</v>
       </c>
       <c r="D15" t="n">
-        <v>154.9909592081345</v>
+        <v>98.32869231659333</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>INE292B01021</t>
+          <t>INE134E01011</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>-14.75409836065574</v>
+        <v>-17.21311475409836</v>
       </c>
       <c r="H15" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="I15" t="n">
         <v>80</v>
       </c>
       <c r="J15" t="n">
-        <v>266.9</v>
+        <v>251.9</v>
       </c>
       <c r="K15" t="n">
         <v>14</v>
@@ -1097,37 +1097,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>57.37704918032787</v>
       </c>
       <c r="C16" t="n">
-        <v>40.16393442622951</v>
+        <v>42.62295081967213</v>
       </c>
       <c r="D16" t="n">
-        <v>98.32869231659333</v>
+        <v>154.9909592081345</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>INE134E01011</t>
+          <t>INE292B01021</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>-17.21311475409836</v>
+        <v>-14.75409836065574</v>
       </c>
       <c r="H16" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="I16" t="n">
         <v>80</v>
       </c>
       <c r="J16" t="n">
-        <v>251.9</v>
+        <v>266.9</v>
       </c>
       <c r="K16" t="n">
         <v>15</v>
